--- a/plantilla/mcu5/excel/01-controles-mcu5-perfil-avanzado.xlsx
+++ b/plantilla/mcu5/excel/01-controles-mcu5-perfil-avanzado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controles MCU5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Controles MCU5" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,16 +506,20 @@
           <t>Política de ciberseguridad aprobada y comunicada</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Política firmada</t>
+          <t>docs/01-Politica-Seguridad.md (borrador v0.1)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Presentar la política aprobada con fecha y firma de la Dirección</t>
+          <t>Mostrar el documento y su historial de versiones; aprobacion formal del RSI pendiente antes del 14/10.</t>
         </is>
       </c>
     </row>
@@ -530,16 +534,20 @@
           <t>Estrategia de ciberseguridad alineada al negocio</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Estrategia/plan anual</t>
+          <t>LETRA.md (RF/RNF) + docs/00-arquitectura-4mas1.md y docs/00-arquitectura-c4.md</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Mostrar el plan anual y su presentación a la Dirección</t>
+          <t>Mostrar como cada RF/RNF se refleja en la arquitectura y en los hitos H1-H5 del README.</t>
         </is>
       </c>
     </row>
@@ -554,16 +562,20 @@
           <t>Roles y responsabilidades claros (RSI, comité, dueños)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Matriz RACI / organigrama</t>
+          <t>plantilla/mcu5/excel/03-matriz-raci-mcu5.xlsx (completa)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Desplegar la matriz RACI con responsables por proceso</t>
+          <t>Desplegar la RACI: Horacio Duarte, Pablo Morales y Andres Varela por proceso.</t>
         </is>
       </c>
     </row>
@@ -578,16 +590,20 @@
           <t>Programa de gestión de riesgo institucional</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Análisis de riesgos</t>
+          <t>docs/03-Analisis-Riesgos.md</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Presentar matriz de riesgos con tratamiento y riesgo residual aceptado</t>
+          <t>Mostrar los 12 riesgos (R01-R12) con tratamiento y la seccion de riesgo residual.</t>
         </is>
       </c>
     </row>
@@ -602,16 +618,20 @@
           <t>Gestión de cadena de suministro y terceros</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Análisis de dependencias</t>
+          <t>docs/02-Registro-Activos.md + requirements.txt / Cargo.toml / package.json (versiones fijadas)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Listar servidores/proveedores y su evaluación</t>
+          <t>Mostrar que las dependencias externas (Wazuh, Mailu, PostgreSQL, librerias) estan inventariadas y con version pineada, no 'latest'.</t>
         </is>
       </c>
     </row>
@@ -626,16 +646,20 @@
           <t>Marco de cumplimiento (MCU5, BCU, ISO, COBIT, URCDP)</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>SoA + brecha MCU</t>
+          <t>Encabezados de mapeo normativo de cada doc en docs/ + docs/11-SoA-Plan-Tratamiento.md (pendiente)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Mostrar la SoA y la brecha por función con perfil Avanzado</t>
+          <t>Mostrar el mapeo normativo de cada documento; la SoA formal se completa en el cierre (05-07/10).</t>
         </is>
       </c>
     </row>
@@ -650,16 +674,24 @@
           <t>Presupuesto y recursos de seguridad</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>N.A.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Proyecto academico sin presupuesto monetario formal: los recursos son las horas del equipo (3 personas), gestionadas y trazadas en docs/99-bitacora-trabajo.md, no en un plan de inversion corporativo.</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Plan de inversión</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Presentar carta con dotación de recursos</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -674,16 +706,20 @@
           <t>Revisión periódica de gobierno por la Dirección</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Actas de comité</t>
+          <t>docs/99-bitacora-trabajo.md (entradas por hito)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Mostrar actas de reuniones de seguimiento</t>
+          <t>Mostrar las entradas de bitacora de cada hito (H1-H5) como equivalente de la revision de gobierno, con Andres Varela como RSI dando seguimiento.</t>
         </is>
       </c>
     </row>
@@ -698,16 +734,20 @@
           <t>Inventario de activos de información</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Registro de activos (Excel MCU)</t>
+          <t>plantilla/mcu5/excel/02-registro-activos-mcu5.xlsx + docs/02-Registro-Activos.md (14 activos)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Desplegar el Excel de activos completo y actualizado</t>
+          <t>Desplegar el Excel de activos completo y actualizado.</t>
         </is>
       </c>
     </row>
@@ -722,16 +762,20 @@
           <t>Propietarios de activos y clasificación</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Registro de activos</t>
+          <t>docs/02-Registro-Activos.md (columnas Dueno / Clasificacion)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Mostrar que cada activo tiene dueño y clasificación</t>
+          <t>Mostrar que cada uno de los 14 activos tiene dueno y clasificacion asignada.</t>
         </is>
       </c>
     </row>
@@ -746,16 +790,20 @@
           <t>Análisis de impacto en el negocio (BIA)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Matriz de criticidad</t>
+          <t>docs/02-Registro-Activos.md, seccion 5 (matriz critica con RTO por proceso)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Presentar procesos críticos y activos que los soportan</t>
+          <t>Presentar la matriz critica y los RTO declarados (ej. &lt;2s reapertura local, 4h control central).</t>
         </is>
       </c>
     </row>
@@ -770,16 +818,20 @@
           <t>Evaluación de riesgos de ciberseguridad</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Análisis de riesgos</t>
+          <t>docs/03-Analisis-Riesgos.md (matriz 5x5, R01-R12)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Presentar matriz 5x5 con tratamiento del riesgo</t>
+          <t>Recorrer la matriz de riesgo y el nivel asignado a cada uno.</t>
         </is>
       </c>
     </row>
@@ -794,16 +846,20 @@
           <t>Comunicación y aceptación de riesgos</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Acta de aceptación</t>
+          <t>docs/03-Analisis-Riesgos.md, seccion 6 (riesgo residual)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Mostrar riesgo residual aceptado y firmado</t>
+          <t>Mostrar la seccion 6 con fechas objetivo cargadas; la aceptacion formal (firma del RSI) es un pendiente explicito antes del 07/10.</t>
         </is>
       </c>
     </row>
@@ -818,16 +874,20 @@
           <t>Inventario de vulnerabilidades</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Registro de vulnerabilidades</t>
+          <t>docs/10-Gestion-Vulnerabilidades.md (pendiente de escribir, meta 01-05/10)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Desplegar el registro con CVSS y estado</t>
+          <t>Pendiente: requiere correr escaneos SAST/DAST/OpenVAS antes de poder demostrarlo.</t>
         </is>
       </c>
     </row>
@@ -842,16 +902,20 @@
           <t>Mapa de datos personales (URCDP)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Registro de bases de datos</t>
+          <t>docs/02-Registro-Activos.md, activos con 'Dato personal = S' (A02, A05, A07, A10)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Listar bases con datos personales y su tratamiento</t>
+          <t>Filtrar el registro de activos por esa columna y mostrar los 4 activos marcados.</t>
         </is>
       </c>
     </row>
@@ -866,16 +930,20 @@
           <t>Identificación de dependencias externas</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Diagrama de arquitectura</t>
+          <t>docs/00-arquitectura-c4.md (nivel 1 y 2) + diagrama de comunicacion (artifact publicado)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Mostrar servicios externos/integrados en el diagrama</t>
+          <t>Mostrar el diagrama C4 (actores externos: Mailu, Wazuh, RSI/Auditor) y el mapa de eventos.</t>
         </is>
       </c>
     </row>
@@ -890,16 +958,20 @@
           <t>Gestión de identidades y credenciales</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Configuración IAM</t>
+          <t>docs/09-Gestion-Accesos.md</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Demostrar alta/baja de usuarios y políticas de credenciales</t>
+          <t>Pendiente de implementacion: RBAC de control-central/app/api/users.py sigue siendo un TODO. Hoy se demuestra el diseno, no el alta/baja real.</t>
         </is>
       </c>
     </row>
@@ -914,16 +986,20 @@
           <t>Autenticación multifactor (TOTP/WebAuthn/Hello)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Config. + capturas</t>
+          <t>docs/09-Gestion-Accesos.md, tabla 'Evidencia pendiente'</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Registrar login con 2 factores en vivo</t>
+          <t>Pendiente: TOTP/WebAuthn/Windows Hello no implementados aun (meta H3, 02/10); no se puede demostrar en vivo hoy.</t>
         </is>
       </c>
     </row>
@@ -938,16 +1014,20 @@
           <t>Revisión de privilegios (mínimo privilegio)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Matriz de accesos</t>
+          <t>Diseno de clave JWS unica por agente (cliente-gestor/src-tauri/src/events/signer.rs) + RBAC de control-central (pendiente)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Mostrar revisión periódica de privilegios</t>
+          <t>Pendiente de despliegue: mostrar que un agente comprometido no puede firmar eventos de otro (R02 en 03-Analisis-Riesgos.md).</t>
         </is>
       </c>
     </row>
@@ -962,16 +1042,20 @@
           <t>Protección de datos (cifrado en reposo y en tránsito)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Cifrado de BD y TLS</t>
+          <t>cliente-gestor/src-tauri/src/crypto/ (Argon2id + XChaCha20-Poly1305, hoy son stubs con TODO)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Demostrar cifrado de bóveda/BD y TLS 1.2+</t>
+          <t>Pendiente de implementacion real; hoy kdf.rs y cipher.rs no tienen logica. TLS 1.2+ en transito tambien pendiente de desplegar.</t>
         </is>
       </c>
     </row>
@@ -986,16 +1070,20 @@
           <t>Respaldos y prueba de restauración</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Registro de backup</t>
+          <t>docs/06-Plan-Continuidad.md (pendiente, meta 28/09-01/10)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Restaurar un respaldo en vivo ante la auditoría</t>
+          <t>Pendiente: falta escribir el plan y ejecutar una prueba de restauracion real.</t>
         </is>
       </c>
     </row>
@@ -1010,16 +1098,20 @@
           <t>Capacitación y concientización del personal</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Plan de capacitación</t>
+          <t>docs/99-bitacora-trabajo.md, entrada 'Analisis de la letra y definicion de arquitectura/stack' (15/09/2026)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Presentar plan y registro de asistencia</t>
+          <t>Mostrar esa entrada de bitacora como induccion/capacitacion inicial del equipo de 3 personas.</t>
         </is>
       </c>
     </row>
@@ -1034,16 +1126,20 @@
           <t>Configuración segura de sistemas</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Config. endurecida</t>
+          <t>control-central/Dockerfile + infra/docker-compose.yml</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Mostrar hardening por checklist</t>
+          <t>Pendiente de hardening real: hoy es un Dockerfile basico (python:3.12-slim) sin checklist de endurecimiento aplicado.</t>
         </is>
       </c>
     </row>
@@ -1058,16 +1154,20 @@
           <t>Mantenimiento y parcheo</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Historial de parches</t>
+          <t>requirements.txt / Cargo.toml / package.json (versiones exactas, no rangos abiertos)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Mostrar aplicaciones de parches en el período</t>
+          <t>Mostrar que las versiones estan fijadas; falta un proceso periodico formal de actualizacion de dependencias.</t>
         </is>
       </c>
     </row>
@@ -1082,16 +1182,20 @@
           <t>Protección de endpoints (HIDS/antivirus/EDR)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Agentes activos</t>
+          <t>infra/wazuh/README.md (agente Wazuh planificado en el cliente)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Mostrar agentes HIDS conectados al SIEM</t>
+          <t>Pendiente: Wazuh todavia no esta desplegado (meta H2, 29/09).</t>
         </is>
       </c>
     </row>
@@ -1106,16 +1210,20 @@
           <t>Protección de la red (firewalls, segmentación, IDS/IPS)</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Diagrama + reglas</t>
+          <t>docs/02-Registro-Activos.md (A14, segmentacion de red) + docs/00-arquitectura-4mas1.md (vista fisica)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Presentar reglas de firewall y segmentación en vivo</t>
+          <t>Mostrar la segmentacion de VLANs planificada. El equipo decidio NO implementar Security Onion/NIDS (opcional en la letra); IDS/IPS de red queda fuera de alcance por esa decision documentada.</t>
         </is>
       </c>
     </row>
@@ -1130,16 +1238,20 @@
           <t>Gestión de vulnerabilidades técnicas</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Escaneos + cierre</t>
+          <t>docs/10-Gestion-Vulnerabilidades.md (pendiente)</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Mostrar escaneos y resolución con plazos</t>
+          <t>Pendiente: requiere escaneos y su cierre con plazos, aun no realizados.</t>
         </is>
       </c>
     </row>
@@ -1154,16 +1266,20 @@
           <t>Seguridad en el ciclo de desarrollo (SAST)</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Informe SAST</t>
+          <t>Pendiente: ningun SAST (semgrep/bandit) corrido aun sobre control-central</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Mostrar informe de semgrep/bandit sin hallazgos críticos</t>
+          <t>Vinculado a R03 y R10 de docs/03-Analisis-Riesgos.md; se demuestra cuando exista un informe SAST sin hallazgos criticos, antes del 05/10.</t>
         </is>
       </c>
     </row>
@@ -1178,16 +1294,24 @@
           <t>Monitoreo continuo de la red (NIDS)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>N.A.</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>El equipo decidio no implementar Security Onion/Suricata/Zeek (NIDS), explicitamente opcional en la letra, para priorizar Wazuh (HIDS/SIEM) dado el tiempo disponible. La deteccion se concentra en host, no en red.</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Reglas Suricata/Zeek</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Mostrar eventos de red capturados recientemente</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1202,16 +1326,20 @@
           <t>Monitoreo de hosts (HIDS/FIM)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Alertas Wazuh</t>
+          <t>infra/wazuh/README.md (agente Wazuh, FIM sobre el archivo de boveda)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Mostrar monitoreo de integridad de archivos</t>
+          <t>Pendiente de despliegue (meta H2, 29/09).</t>
         </is>
       </c>
     </row>
@@ -1226,16 +1354,20 @@
           <t>Correlación de eventos (SIEM)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Dashboards SIEM</t>
+          <t>infra/docker-compose.yml (Wazuh externo) + control-central/app/siem/wazuh_forwarder.py</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Presentar dashboard con eventos correlacionados</t>
+          <t>Pendiente: el forwarder es hoy un stub sin logica de reenvio real.</t>
         </is>
       </c>
     </row>
@@ -1250,16 +1382,20 @@
           <t>Firmas y reglas de detección actualizadas</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Versión de firmas</t>
+          <t>Reglas custom de Wazuh (fuerza bruta de maestra, borrado masivo, cambio de maestra) documentadas en infra/wazuh/README.md</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Mostrar fecha de actualización de firmas</t>
+          <t>Pendiente de creacion real (meta 28/09-01/10, ver docs/07-Monitoreo-Logs-SIEM.md, aun sin escribir).</t>
         </is>
       </c>
     </row>
@@ -1274,16 +1410,20 @@
           <t>Pruebas de detección (ejercicios púrpura/red team)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Evidencia de simulación</t>
+          <t>Se cubre en la Parte 2 (Red Team, 28/10-09/11/2026)</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Presentar al menos un ataque simulado detectado</t>
+          <t>No aplica plenamente en esta fase del Blue Team; se demuestra con un ataque simulado propio antes del 14/10 o con el resultado del Red Team el 09/11.</t>
         </is>
       </c>
     </row>
@@ -1298,16 +1438,20 @@
           <t>Detección de anomalías de comportamiento</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Regla de anomalía</t>
+          <t>Regla Wazuh de fuerza bruta de maestra (delay adaptativo + alerta), ligada a R01 de docs/03-Analisis-Riesgos.md</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Mostrar una regla de comportamiento y su alerta</t>
+          <t>Pendiente de implementacion.</t>
         </is>
       </c>
     </row>
@@ -1322,16 +1466,20 @@
           <t>Alerta y notificación oportuna</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Canales de alerta</t>
+          <t>Mailu (correo, RF-07)</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Demostrar una alerta por mail/webhook/llamada</t>
+          <t>Pendiente de despliegue de Mailu (meta 29/09) y de disparar un correo real de prueba ante un evento de alta/cambio de maestra.</t>
         </is>
       </c>
     </row>
@@ -1346,16 +1494,20 @@
           <t>Monitoreo de los controles de protección</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Estado de controles</t>
+          <t>Grafana (dashboard, RF-09/RF-14: agentes activos, estado del servidor de mail)</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Mostrar salud de firewalls/agentes en el dashboard</t>
+          <t>Pendiente: infra/grafana/provisioning/ todavia no tiene datasources ni dashboards cargados.</t>
         </is>
       </c>
     </row>
@@ -1370,16 +1522,20 @@
           <t>Plan de respuesta a incidentes</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Procedimiento de incidentes</t>
+          <t>docs/04-Gestion-Incidentes.md (pendiente, meta 02-05/10)</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Exponer el plan y sus fases</t>
+          <t>Pendiente de escribir.</t>
         </is>
       </c>
     </row>
@@ -1394,16 +1550,20 @@
           <t>Roles y comunicación en respuesta</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Matriz de comunicación</t>
+          <t>plantilla/mcu5/excel/03-matriz-raci-mcu5.xlsx, fila 'Gestion de incidentes'</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Mostrar responsables de comunicación y escalamiento</t>
+          <t>Mostrar la fila de la RACI: Andres Varela como R/A, Horacio Duarte y Pablo Morales consultados segun el componente afectado.</t>
         </is>
       </c>
     </row>
@@ -1418,16 +1578,20 @@
           <t>Análisis y contención de incidentes</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Registros de incidentes</t>
+          <t>docs/04-Gestion-Incidentes.md + registro de incidente simulado (entregable de la seccion 6.2 de LETRA.md, pendiente)</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Presentar un incidente completo (detección a cierre)</t>
+          <t>Pendiente: falta simular al menos un incidente completo (deteccion a cierre) antes del 07/10.</t>
         </is>
       </c>
     </row>
@@ -1442,16 +1606,20 @@
           <t>Erradicación y recuperación</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Incidente resuelto</t>
+          <t>docs/04-Gestion-Incidentes.md (pendiente)</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Mostrar evidencia de la mitigación</t>
+          <t>Pendiente, depende del incidente simulado.</t>
         </is>
       </c>
     </row>
@@ -1466,16 +1634,20 @@
           <t>Notificación a autoridades (BCU, URCDP, CERTuy)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Borradores de notificación</t>
+          <t>docs/12-Notificacion-Incidentes.md (pendiente, meta 05-07/10)</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Presentar notificación simulada completa</t>
+          <t>Pendiente de escribir; se basa en un borrador de notificacion simulada BCU/URCDP.</t>
         </is>
       </c>
     </row>
@@ -1490,16 +1662,20 @@
           <t>Lecciones aprendidas y mejora</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Informe de lecciones</t>
+          <t>docs/99-bitacora-trabajo.md + foro de lecciones aprendidas del 09/11 (seccion 8.4 de LETRA.md)</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Mostrar acciones correctivas aplicadas</t>
+          <t>No aplica plenamente hasta el cierre del curso; en la auditoria del 14/10 se muestra el mecanismo (bitacora), aunque todavia no haya lecciones de un hallazgo real del Red Team.</t>
         </is>
       </c>
     </row>
@@ -1514,16 +1690,20 @@
           <t>Plan de recuperación (BCP/DRP)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Plan de continuidad</t>
+          <t>docs/06-Plan-Continuidad.md (pendiente, meta 28/09-01/10)</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Exponer el BCP/DRP con RTO/RPO</t>
+          <t>Pendiente de escribir y de ejecutar una prueba de restauracion.</t>
         </is>
       </c>
     </row>
@@ -1538,16 +1718,20 @@
           <t>Comunicación de crisis</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Procedimiento de crisis</t>
+          <t>Mailu (correo) + docs/99-bitacora-trabajo.md; no se implementa Wazo (telefonia), opcional en la letra</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Presentar canales y responsables de crisis</t>
+          <t>La comunicacion de crisis se limita a correo y bitacora del equipo; se aclara la ausencia de canal telefonico como decision de alcance.</t>
         </is>
       </c>
     </row>
@@ -1562,16 +1746,20 @@
           <t>Restauración de respaldos validada</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Prueba de restauración</t>
+          <t>docs/06-Plan-Continuidad.md (pendiente)</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Ejecutar/evidenciar una restauración real</t>
+          <t>Pendiente: requiere ejecutar una restauracion real de un backup de PostgreSQL o de una boveda exportada.</t>
         </is>
       </c>
     </row>
@@ -1586,16 +1774,20 @@
           <t>Reanudación de operaciones</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Plan de retorno</t>
+          <t>docs/06-Plan-Continuidad.md (pendiente)</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Mostrar secuencia de reanudación de servicios</t>
+          <t>Pendiente de escribir la secuencia de reanudacion de servicios.</t>
         </is>
       </c>
     </row>
@@ -1610,16 +1802,20 @@
           <t>Mejora continua post-recuperación</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Acciones de mejora</t>
+          <t>docs/99-bitacora-trabajo.md + foro de lecciones aprendidas (09/11)</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Presentar mejoras aplicadas tras las simulaciones</t>
+          <t>No aplica plenamente hasta el cierre; se muestra el mecanismo de mejora continua (bitacora).</t>
         </is>
       </c>
     </row>

--- a/plantilla/mcu5/excel/01-controles-mcu5-perfil-avanzado.xlsx
+++ b/plantilla/mcu5/excel/01-controles-mcu5-perfil-avanzado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Controles MCU5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controles MCU5" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,20 +506,16 @@
           <t>Política de ciberseguridad aprobada y comunicada</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>docs/01-Politica-Seguridad.md (borrador v0.1)</t>
+          <t>Política firmada</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Mostrar el documento y su historial de versiones; aprobacion formal del RSI pendiente antes del 14/10.</t>
+          <t>Presentar la política aprobada con fecha y firma de la Dirección</t>
         </is>
       </c>
     </row>
@@ -534,20 +530,16 @@
           <t>Estrategia de ciberseguridad alineada al negocio</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>LETRA.md (RF/RNF) + docs/00-arquitectura-4mas1.md y docs/00-arquitectura-c4.md</t>
+          <t>Estrategia/plan anual</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Mostrar como cada RF/RNF se refleja en la arquitectura y en los hitos H1-H5 del README.</t>
+          <t>Mostrar el plan anual y su presentación a la Dirección</t>
         </is>
       </c>
     </row>
@@ -562,20 +554,16 @@
           <t>Roles y responsabilidades claros (RSI, comité, dueños)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>plantilla/mcu5/excel/03-matriz-raci-mcu5.xlsx (completa)</t>
+          <t>Matriz RACI / organigrama</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Desplegar la RACI: Horacio Duarte, Pablo Morales y Andres Varela por proceso.</t>
+          <t>Desplegar la matriz RACI con responsables por proceso</t>
         </is>
       </c>
     </row>
@@ -590,20 +578,16 @@
           <t>Programa de gestión de riesgo institucional</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>docs/03-Analisis-Riesgos.md</t>
+          <t>Análisis de riesgos</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Mostrar los 12 riesgos (R01-R12) con tratamiento y la seccion de riesgo residual.</t>
+          <t>Presentar matriz de riesgos con tratamiento y riesgo residual aceptado</t>
         </is>
       </c>
     </row>
@@ -618,20 +602,16 @@
           <t>Gestión de cadena de suministro y terceros</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>docs/02-Registro-Activos.md + requirements.txt / Cargo.toml / package.json (versiones fijadas)</t>
+          <t>Análisis de dependencias</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Mostrar que las dependencias externas (Wazuh, Mailu, PostgreSQL, librerias) estan inventariadas y con version pineada, no 'latest'.</t>
+          <t>Listar servidores/proveedores y su evaluación</t>
         </is>
       </c>
     </row>
@@ -646,20 +626,16 @@
           <t>Marco de cumplimiento (MCU5, BCU, ISO, COBIT, URCDP)</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Encabezados de mapeo normativo de cada doc en docs/ + docs/11-SoA-Plan-Tratamiento.md (pendiente)</t>
+          <t>SoA + brecha MCU</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Mostrar el mapeo normativo de cada documento; la SoA formal se completa en el cierre (05-07/10).</t>
+          <t>Mostrar la SoA y la brecha por función con perfil Avanzado</t>
         </is>
       </c>
     </row>
@@ -674,24 +650,16 @@
           <t>Presupuesto y recursos de seguridad</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>N.A.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Proyecto academico sin presupuesto monetario formal: los recursos son las horas del equipo (3 personas), gestionadas y trazadas en docs/99-bitacora-trabajo.md, no en un plan de inversion corporativo.</t>
-        </is>
-      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Plan de inversión</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Presentar carta con dotación de recursos</t>
         </is>
       </c>
     </row>
@@ -706,20 +674,16 @@
           <t>Revisión periódica de gobierno por la Dirección</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>docs/99-bitacora-trabajo.md (entradas por hito)</t>
+          <t>Actas de comité</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Mostrar las entradas de bitacora de cada hito (H1-H5) como equivalente de la revision de gobierno, con Andres Varela como RSI dando seguimiento.</t>
+          <t>Mostrar actas de reuniones de seguimiento</t>
         </is>
       </c>
     </row>
@@ -734,20 +698,16 @@
           <t>Inventario de activos de información</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>plantilla/mcu5/excel/02-registro-activos-mcu5.xlsx + docs/02-Registro-Activos.md (14 activos)</t>
+          <t>Registro de activos (Excel MCU)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Desplegar el Excel de activos completo y actualizado.</t>
+          <t>Desplegar el Excel de activos completo y actualizado</t>
         </is>
       </c>
     </row>
@@ -762,20 +722,16 @@
           <t>Propietarios de activos y clasificación</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>docs/02-Registro-Activos.md (columnas Dueno / Clasificacion)</t>
+          <t>Registro de activos</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Mostrar que cada uno de los 14 activos tiene dueno y clasificacion asignada.</t>
+          <t>Mostrar que cada activo tiene dueño y clasificación</t>
         </is>
       </c>
     </row>
@@ -790,20 +746,16 @@
           <t>Análisis de impacto en el negocio (BIA)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>docs/02-Registro-Activos.md, seccion 5 (matriz critica con RTO por proceso)</t>
+          <t>Matriz de criticidad</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Presentar la matriz critica y los RTO declarados (ej. &lt;2s reapertura local, 4h control central).</t>
+          <t>Presentar procesos críticos y activos que los soportan</t>
         </is>
       </c>
     </row>
@@ -818,20 +770,16 @@
           <t>Evaluación de riesgos de ciberseguridad</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>docs/03-Analisis-Riesgos.md (matriz 5x5, R01-R12)</t>
+          <t>Análisis de riesgos</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Recorrer la matriz de riesgo y el nivel asignado a cada uno.</t>
+          <t>Presentar matriz 5x5 con tratamiento del riesgo</t>
         </is>
       </c>
     </row>
@@ -846,20 +794,16 @@
           <t>Comunicación y aceptación de riesgos</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>docs/03-Analisis-Riesgos.md, seccion 6 (riesgo residual)</t>
+          <t>Acta de aceptación</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Mostrar la seccion 6 con fechas objetivo cargadas; la aceptacion formal (firma del RSI) es un pendiente explicito antes del 07/10.</t>
+          <t>Mostrar riesgo residual aceptado y firmado</t>
         </is>
       </c>
     </row>
@@ -874,20 +818,16 @@
           <t>Inventario de vulnerabilidades</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>docs/10-Gestion-Vulnerabilidades.md (pendiente de escribir, meta 01-05/10)</t>
+          <t>Registro de vulnerabilidades</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: requiere correr escaneos SAST/DAST/OpenVAS antes de poder demostrarlo.</t>
+          <t>Desplegar el registro con CVSS y estado</t>
         </is>
       </c>
     </row>
@@ -902,20 +842,16 @@
           <t>Mapa de datos personales (URCDP)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>docs/02-Registro-Activos.md, activos con 'Dato personal = S' (A02, A05, A07, A10)</t>
+          <t>Registro de bases de datos</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Filtrar el registro de activos por esa columna y mostrar los 4 activos marcados.</t>
+          <t>Listar bases con datos personales y su tratamiento</t>
         </is>
       </c>
     </row>
@@ -930,20 +866,16 @@
           <t>Identificación de dependencias externas</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>docs/00-arquitectura-c4.md (nivel 1 y 2) + diagrama de comunicacion (artifact publicado)</t>
+          <t>Diagrama de arquitectura</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Mostrar el diagrama C4 (actores externos: Mailu, Wazuh, RSI/Auditor) y el mapa de eventos.</t>
+          <t>Mostrar servicios externos/integrados en el diagrama</t>
         </is>
       </c>
     </row>
@@ -958,20 +890,16 @@
           <t>Gestión de identidades y credenciales</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>docs/09-Gestion-Accesos.md</t>
+          <t>Configuración IAM</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de implementacion: RBAC de control-central/app/api/users.py sigue siendo un TODO. Hoy se demuestra el diseno, no el alta/baja real.</t>
+          <t>Demostrar alta/baja de usuarios y políticas de credenciales</t>
         </is>
       </c>
     </row>
@@ -986,20 +914,16 @@
           <t>Autenticación multifactor (TOTP/WebAuthn/Hello)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>docs/09-Gestion-Accesos.md, tabla 'Evidencia pendiente'</t>
+          <t>Config. + capturas</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: TOTP/WebAuthn/Windows Hello no implementados aun (meta H3, 02/10); no se puede demostrar en vivo hoy.</t>
+          <t>Registrar login con 2 factores en vivo</t>
         </is>
       </c>
     </row>
@@ -1014,20 +938,16 @@
           <t>Revisión de privilegios (mínimo privilegio)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Diseno de clave JWS unica por agente (cliente-gestor/src-tauri/src/events/signer.rs) + RBAC de control-central (pendiente)</t>
+          <t>Matriz de accesos</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de despliegue: mostrar que un agente comprometido no puede firmar eventos de otro (R02 en 03-Analisis-Riesgos.md).</t>
+          <t>Mostrar revisión periódica de privilegios</t>
         </is>
       </c>
     </row>
@@ -1042,20 +962,16 @@
           <t>Protección de datos (cifrado en reposo y en tránsito)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>cliente-gestor/src-tauri/src/crypto/ (Argon2id + XChaCha20-Poly1305, hoy son stubs con TODO)</t>
+          <t>Cifrado de BD y TLS</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de implementacion real; hoy kdf.rs y cipher.rs no tienen logica. TLS 1.2+ en transito tambien pendiente de desplegar.</t>
+          <t>Demostrar cifrado de bóveda/BD y TLS 1.2+</t>
         </is>
       </c>
     </row>
@@ -1070,20 +986,16 @@
           <t>Respaldos y prueba de restauración</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>docs/06-Plan-Continuidad.md (pendiente, meta 28/09-01/10)</t>
+          <t>Registro de backup</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: falta escribir el plan y ejecutar una prueba de restauracion real.</t>
+          <t>Restaurar un respaldo en vivo ante la auditoría</t>
         </is>
       </c>
     </row>
@@ -1098,20 +1010,16 @@
           <t>Capacitación y concientización del personal</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>docs/99-bitacora-trabajo.md, entrada 'Analisis de la letra y definicion de arquitectura/stack' (15/09/2026)</t>
+          <t>Plan de capacitación</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Mostrar esa entrada de bitacora como induccion/capacitacion inicial del equipo de 3 personas.</t>
+          <t>Presentar plan y registro de asistencia</t>
         </is>
       </c>
     </row>
@@ -1126,20 +1034,16 @@
           <t>Configuración segura de sistemas</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>control-central/Dockerfile + infra/docker-compose.yml</t>
+          <t>Config. endurecida</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de hardening real: hoy es un Dockerfile basico (python:3.12-slim) sin checklist de endurecimiento aplicado.</t>
+          <t>Mostrar hardening por checklist</t>
         </is>
       </c>
     </row>
@@ -1154,20 +1058,16 @@
           <t>Mantenimiento y parcheo</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>requirements.txt / Cargo.toml / package.json (versiones exactas, no rangos abiertos)</t>
+          <t>Historial de parches</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Mostrar que las versiones estan fijadas; falta un proceso periodico formal de actualizacion de dependencias.</t>
+          <t>Mostrar aplicaciones de parches en el período</t>
         </is>
       </c>
     </row>
@@ -1182,20 +1082,16 @@
           <t>Protección de endpoints (HIDS/antivirus/EDR)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>infra/wazuh/README.md (agente Wazuh planificado en el cliente)</t>
+          <t>Agentes activos</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: Wazuh todavia no esta desplegado (meta H2, 29/09).</t>
+          <t>Mostrar agentes HIDS conectados al SIEM</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1106,16 @@
           <t>Protección de la red (firewalls, segmentación, IDS/IPS)</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>docs/02-Registro-Activos.md (A14, segmentacion de red) + docs/00-arquitectura-4mas1.md (vista fisica)</t>
+          <t>Diagrama + reglas</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Mostrar la segmentacion de VLANs planificada. El equipo decidio NO implementar Security Onion/NIDS (opcional en la letra); IDS/IPS de red queda fuera de alcance por esa decision documentada.</t>
+          <t>Presentar reglas de firewall y segmentación en vivo</t>
         </is>
       </c>
     </row>
@@ -1238,20 +1130,16 @@
           <t>Gestión de vulnerabilidades técnicas</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>docs/10-Gestion-Vulnerabilidades.md (pendiente)</t>
+          <t>Escaneos + cierre</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: requiere escaneos y su cierre con plazos, aun no realizados.</t>
+          <t>Mostrar escaneos y resolución con plazos</t>
         </is>
       </c>
     </row>
@@ -1266,20 +1154,16 @@
           <t>Seguridad en el ciclo de desarrollo (SAST)</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: ningun SAST (semgrep/bandit) corrido aun sobre control-central</t>
+          <t>Informe SAST</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Vinculado a R03 y R10 de docs/03-Analisis-Riesgos.md; se demuestra cuando exista un informe SAST sin hallazgos criticos, antes del 05/10.</t>
+          <t>Mostrar informe de semgrep/bandit sin hallazgos críticos</t>
         </is>
       </c>
     </row>
@@ -1294,24 +1178,16 @@
           <t>Monitoreo continuo de la red (NIDS)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>N.A.</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>El equipo decidio no implementar Security Onion/Suricata/Zeek (NIDS), explicitamente opcional en la letra, para priorizar Wazuh (HIDS/SIEM) dado el tiempo disponible. La deteccion se concentra en host, no en red.</t>
-        </is>
-      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Reglas Suricata/Zeek</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Mostrar eventos de red capturados recientemente</t>
         </is>
       </c>
     </row>
@@ -1326,20 +1202,16 @@
           <t>Monitoreo de hosts (HIDS/FIM)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>infra/wazuh/README.md (agente Wazuh, FIM sobre el archivo de boveda)</t>
+          <t>Alertas Wazuh</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de despliegue (meta H2, 29/09).</t>
+          <t>Mostrar monitoreo de integridad de archivos</t>
         </is>
       </c>
     </row>
@@ -1354,20 +1226,16 @@
           <t>Correlación de eventos (SIEM)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>infra/docker-compose.yml (Wazuh externo) + control-central/app/siem/wazuh_forwarder.py</t>
+          <t>Dashboards SIEM</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: el forwarder es hoy un stub sin logica de reenvio real.</t>
+          <t>Presentar dashboard con eventos correlacionados</t>
         </is>
       </c>
     </row>
@@ -1382,20 +1250,16 @@
           <t>Firmas y reglas de detección actualizadas</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Reglas custom de Wazuh (fuerza bruta de maestra, borrado masivo, cambio de maestra) documentadas en infra/wazuh/README.md</t>
+          <t>Versión de firmas</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de creacion real (meta 28/09-01/10, ver docs/07-Monitoreo-Logs-SIEM.md, aun sin escribir).</t>
+          <t>Mostrar fecha de actualización de firmas</t>
         </is>
       </c>
     </row>
@@ -1410,20 +1274,16 @@
           <t>Pruebas de detección (ejercicios púrpura/red team)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Se cubre en la Parte 2 (Red Team, 28/10-09/11/2026)</t>
+          <t>Evidencia de simulación</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>No aplica plenamente en esta fase del Blue Team; se demuestra con un ataque simulado propio antes del 14/10 o con el resultado del Red Team el 09/11.</t>
+          <t>Presentar al menos un ataque simulado detectado</t>
         </is>
       </c>
     </row>
@@ -1438,20 +1298,16 @@
           <t>Detección de anomalías de comportamiento</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Regla Wazuh de fuerza bruta de maestra (delay adaptativo + alerta), ligada a R01 de docs/03-Analisis-Riesgos.md</t>
+          <t>Regla de anomalía</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de implementacion.</t>
+          <t>Mostrar una regla de comportamiento y su alerta</t>
         </is>
       </c>
     </row>
@@ -1466,20 +1322,16 @@
           <t>Alerta y notificación oportuna</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Mailu (correo, RF-07)</t>
+          <t>Canales de alerta</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de despliegue de Mailu (meta 29/09) y de disparar un correo real de prueba ante un evento de alta/cambio de maestra.</t>
+          <t>Demostrar una alerta por mail/webhook/llamada</t>
         </is>
       </c>
     </row>
@@ -1494,20 +1346,16 @@
           <t>Monitoreo de los controles de protección</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Grafana (dashboard, RF-09/RF-14: agentes activos, estado del servidor de mail)</t>
+          <t>Estado de controles</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: infra/grafana/provisioning/ todavia no tiene datasources ni dashboards cargados.</t>
+          <t>Mostrar salud de firewalls/agentes en el dashboard</t>
         </is>
       </c>
     </row>
@@ -1522,20 +1370,16 @@
           <t>Plan de respuesta a incidentes</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>docs/04-Gestion-Incidentes.md (pendiente, meta 02-05/10)</t>
+          <t>Procedimiento de incidentes</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de escribir.</t>
+          <t>Exponer el plan y sus fases</t>
         </is>
       </c>
     </row>
@@ -1550,20 +1394,16 @@
           <t>Roles y comunicación en respuesta</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>plantilla/mcu5/excel/03-matriz-raci-mcu5.xlsx, fila 'Gestion de incidentes'</t>
+          <t>Matriz de comunicación</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Mostrar la fila de la RACI: Andres Varela como R/A, Horacio Duarte y Pablo Morales consultados segun el componente afectado.</t>
+          <t>Mostrar responsables de comunicación y escalamiento</t>
         </is>
       </c>
     </row>
@@ -1578,20 +1418,16 @@
           <t>Análisis y contención de incidentes</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>docs/04-Gestion-Incidentes.md + registro de incidente simulado (entregable de la seccion 6.2 de LETRA.md, pendiente)</t>
+          <t>Registros de incidentes</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: falta simular al menos un incidente completo (deteccion a cierre) antes del 07/10.</t>
+          <t>Presentar un incidente completo (detección a cierre)</t>
         </is>
       </c>
     </row>
@@ -1606,20 +1442,16 @@
           <t>Erradicación y recuperación</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>docs/04-Gestion-Incidentes.md (pendiente)</t>
+          <t>Incidente resuelto</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Pendiente, depende del incidente simulado.</t>
+          <t>Mostrar evidencia de la mitigación</t>
         </is>
       </c>
     </row>
@@ -1634,20 +1466,16 @@
           <t>Notificación a autoridades (BCU, URCDP, CERTuy)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>docs/12-Notificacion-Incidentes.md (pendiente, meta 05-07/10)</t>
+          <t>Borradores de notificación</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de escribir; se basa en un borrador de notificacion simulada BCU/URCDP.</t>
+          <t>Presentar notificación simulada completa</t>
         </is>
       </c>
     </row>
@@ -1662,20 +1490,16 @@
           <t>Lecciones aprendidas y mejora</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>docs/99-bitacora-trabajo.md + foro de lecciones aprendidas del 09/11 (seccion 8.4 de LETRA.md)</t>
+          <t>Informe de lecciones</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>No aplica plenamente hasta el cierre del curso; en la auditoria del 14/10 se muestra el mecanismo (bitacora), aunque todavia no haya lecciones de un hallazgo real del Red Team.</t>
+          <t>Mostrar acciones correctivas aplicadas</t>
         </is>
       </c>
     </row>
@@ -1690,20 +1514,16 @@
           <t>Plan de recuperación (BCP/DRP)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>docs/06-Plan-Continuidad.md (pendiente, meta 28/09-01/10)</t>
+          <t>Plan de continuidad</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de escribir y de ejecutar una prueba de restauracion.</t>
+          <t>Exponer el BCP/DRP con RTO/RPO</t>
         </is>
       </c>
     </row>
@@ -1718,20 +1538,16 @@
           <t>Comunicación de crisis</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Mailu (correo) + docs/99-bitacora-trabajo.md; no se implementa Wazo (telefonia), opcional en la letra</t>
+          <t>Procedimiento de crisis</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>La comunicacion de crisis se limita a correo y bitacora del equipo; se aclara la ausencia de canal telefonico como decision de alcance.</t>
+          <t>Presentar canales y responsables de crisis</t>
         </is>
       </c>
     </row>
@@ -1746,20 +1562,16 @@
           <t>Restauración de respaldos validada</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>docs/06-Plan-Continuidad.md (pendiente)</t>
+          <t>Prueba de restauración</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: requiere ejecutar una restauracion real de un backup de PostgreSQL o de una boveda exportada.</t>
+          <t>Ejecutar/evidenciar una restauración real</t>
         </is>
       </c>
     </row>
@@ -1774,20 +1586,16 @@
           <t>Reanudación de operaciones</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>docs/06-Plan-Continuidad.md (pendiente)</t>
+          <t>Plan de retorno</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de escribir la secuencia de reanudacion de servicios.</t>
+          <t>Mostrar secuencia de reanudación de servicios</t>
         </is>
       </c>
     </row>
@@ -1802,20 +1610,16 @@
           <t>Mejora continua post-recuperación</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
+      <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>docs/99-bitacora-trabajo.md + foro de lecciones aprendidas (09/11)</t>
+          <t>Acciones de mejora</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>No aplica plenamente hasta el cierre; se muestra el mecanismo de mejora continua (bitacora).</t>
+          <t>Presentar mejoras aplicadas tras las simulaciones</t>
         </is>
       </c>
     </row>
